--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>메이크어바디 헬스 PT 미금점</t>
+          <t>자마이카피트니스 분당정자점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>makeabody1@naver.com</t>
+          <t>jamaica_jeongja@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1407-3242</t>
+          <t>0507-1383-8533</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 67 5층</t>
+          <t>경기도 성남시 분당구 정자일로 121 지하 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/make_a__body</t>
+          <t>https://www.instagram.com/jamaica_bundang?igsh=MWY4cGIybjlodW11bw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>470</v>
+        <v>1825</v>
       </c>
       <c r="Q2" t="n">
-        <v>775</v>
+        <v>223</v>
       </c>
       <c r="R2" t="n">
-        <v>1245</v>
+        <v>2048</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1315101138</t>
+          <t>1710539074</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315101138</t>
+          <t>https://m.place.naver.com/place/1710539074</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뉴핏휘트니스 정자점</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>newfit_csj@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1347-6714</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자로76번길 11 한라프라자</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/newfit_csj</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1139</v>
+        <v>2535</v>
       </c>
       <c r="Q3" t="n">
-        <v>962</v>
+        <v>322</v>
       </c>
       <c r="R3" t="n">
-        <v>2101</v>
+        <v>2857</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>36782451</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36782451</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>트랜스핏짐 서현역점</t>
+          <t>스포짐 판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>transfit_gym@naver.com</t>
+          <t>spogym_2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1387-9682</t>
+          <t>0507-1476-8384</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 15 지하1층 트랜스핏짐 서현역점</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/transfit_gym</t>
+          <t>https://www.instagram.com/spogym_pg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2181</v>
+        <v>732</v>
       </c>
       <c r="Q4" t="n">
-        <v>2216</v>
+        <v>624</v>
       </c>
       <c r="R4" t="n">
-        <v>4397</v>
+        <v>1356</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1487183442</t>
+          <t>20123697</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487183442</t>
+          <t>https://m.place.naver.com/place/20123697</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="Q5" t="n">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="R5" t="n">
         <v>2200</v>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kindgym28@naver.com</t>
+          <t>healthboy90_@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1361-3615</t>
+          <t>0507-1419-2436</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 아미고타워 B1층 카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kindgym28</t>
+          <t>https://blog.naver.com/healthboy90_/223799590825</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2034</v>
+        <v>457</v>
       </c>
       <c r="Q6" t="n">
-        <v>1532</v>
+        <v>750</v>
       </c>
       <c r="R6" t="n">
-        <v>3566</v>
+        <v>1207</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>36230651</t>
+          <t>1989525945</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36230651</t>
+          <t>https://m.place.naver.com/place/1989525945</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q7" t="n">
-        <v>984</v>
+        <v>1033</v>
       </c>
       <c r="R7" t="n">
-        <v>1269</v>
+        <v>1317</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>스포애니 수내점</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>spoany012@naver.com</t>
+          <t>dydwk147@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-712-3362</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 364 현대제일상가 B1층</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://m.spoany.co.kr/branch/branch_detail.html?base_seq=MjE=</t>
+          <t>https://blog.naver.com/dydwk147</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1161,19 +1161,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40bmg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>289</v>
+        <v>561</v>
       </c>
       <c r="Q8" t="n">
-        <v>1521</v>
+        <v>1070</v>
       </c>
       <c r="R8" t="n">
-        <v>1810</v>
+        <v>1631</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>31849989</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31849989</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1218,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피트니스 리본</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fitnessreborn@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1376-1546</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 매화로 53 5층 피트니스리본</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,27 +1254,23 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wumh0ut</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1283,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>500</v>
+        <v>1766</v>
       </c>
       <c r="Q9" t="n">
-        <v>88</v>
+        <v>249</v>
       </c>
       <c r="R9" t="n">
-        <v>588</v>
+        <v>2015</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1155595700</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155595700</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>쿼드짐</t>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>quadgym@naver.com</t>
+          <t>londoner83@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1303-9415</t>
+          <t>0507-1406-9679</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/londoner83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,24 +1348,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc5w2o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1381,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>81</v>
+        <v>1341</v>
       </c>
       <c r="Q10" t="n">
-        <v>102</v>
+        <v>473</v>
       </c>
       <c r="R10" t="n">
-        <v>183</v>
+        <v>1814</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>13530251</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/13530251</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1418,74 +1410,74 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1402-7136</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc9u20</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,51 +1486,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>36428321</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428321</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>실내체육관</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>하프미닛 미금</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12round_migeum@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1400-3509</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 25 507, 508호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/halfminute_migeum</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,7 +1545,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1573,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="Q12" t="n">
-        <v>101</v>
+        <v>1437</v>
       </c>
       <c r="R12" t="n">
-        <v>124</v>
+        <v>1579</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1588,17 +1580,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1253552772</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1253552772</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1825</v>
+        <v>1841</v>
       </c>
       <c r="Q2" t="n">
         <v>223</v>
       </c>
       <c r="R2" t="n">
-        <v>2048</v>
+        <v>2064</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>뉴핏휘트니스 정자점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>newfit_csj@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1347-6714</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 정자로76번길 11 한라프라자</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://blog.naver.com/newfit_csj</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2535</v>
+        <v>1137</v>
       </c>
       <c r="Q3" t="n">
-        <v>322</v>
+        <v>965</v>
       </c>
       <c r="R3" t="n">
-        <v>2857</v>
+        <v>2102</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>36782451</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/36782451</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="Q4" t="n">
         <v>624</v>
       </c>
       <c r="R4" t="n">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Q5" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="R5" t="n">
         <v>2200</v>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
+          <t>뭉트니스 야탑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboy90_@naver.com</t>
+          <t>mtns1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1419-2436</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
+          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy90_/223799590825</t>
+          <t>https://www.instagram.com/mtns_leader</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>457</v>
+        <v>284</v>
       </c>
       <c r="Q6" t="n">
-        <v>750</v>
+        <v>1036</v>
       </c>
       <c r="R6" t="n">
-        <v>1207</v>
+        <v>1320</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1989525945</t>
+          <t>1657314482</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989525945</t>
+          <t>https://m.place.naver.com/place/1657314482</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1034,25 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>뭉트니스 야탑</t>
+          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mtns1@naver.com</t>
+          <t>healthboy90_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1419-2436</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mtns_leader</t>
+          <t>https://blog.naver.com/healthboy90_/223799590825</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>284</v>
+        <v>457</v>
       </c>
       <c r="Q7" t="n">
-        <v>1033</v>
+        <v>751</v>
       </c>
       <c r="R7" t="n">
-        <v>1317</v>
+        <v>1208</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,51 +1102,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1657314482</t>
+          <t>1989525945</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657314482</t>
+          <t>https://m.place.naver.com/place/1989525945</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>익스홀릭 가넷 미금점</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dydwk147@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1429-2557</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dydwk147</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>561</v>
+        <v>2540</v>
       </c>
       <c r="Q8" t="n">
-        <v>1070</v>
+        <v>323</v>
       </c>
       <c r="R8" t="n">
-        <v>1631</v>
+        <v>2863</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>12763227</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12763227</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1218,33 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>dydwk147@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/dydwk147</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,7 +1266,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1766</v>
+        <v>561</v>
       </c>
       <c r="Q9" t="n">
-        <v>249</v>
+        <v>1073</v>
       </c>
       <c r="R9" t="n">
-        <v>2015</v>
+        <v>1634</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1334,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londoner83</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,20 +1344,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pnpp</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="Q10" t="n">
         <v>473</v>
       </c>
       <c r="R10" t="n">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1410,38 +1410,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>humblefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1417-1133</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1462,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1471,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1437</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1578</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1508,34 +1504,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1556,7 +1556,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1437</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1579</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,17 +1580,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 지하 1층</t>
+          <t>경기 성남시 분당구 정자일로 121 지하 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsknjve</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자로76번길 11 한라프라자</t>
+          <t>경기 성남시 분당구 정자로76번길 11 한라프라자</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4k06n</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -718,10 +726,10 @@
         <v>1137</v>
       </c>
       <c r="Q3" t="n">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="R3" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+          <t>경기 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpasubw</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
+          <t>경기 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5il7f</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -953,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
+          <t>경기 성남시 분당구 장미로 55 장미마을 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1047,7 +1063,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
+          <t>경기 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1072,10 +1088,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wli4sqi</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1141,7 +1161,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1166,10 +1186,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1235,7 +1259,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1260,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4n5lk</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1278,10 +1306,10 @@
         <v>561</v>
       </c>
       <c r="Q9" t="n">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="R9" t="n">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1329,12 +1357,12 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+          <t>경기 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/londoner83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1344,12 +1372,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1427,7 +1455,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1452,10 +1480,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wnvkt3b</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,104 +1523,6 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>버핏그라운드 PT 판교</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1417-1133</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.butfitground.com/4steppt</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2029680813</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>자마이카피트니스 분당정자점</t>
+          <t>필립발리휘트니스 정자본점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jamaica_jeongja@naver.com</t>
+          <t>ballydesign@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1383-8533</t>
+          <t>031-728-7771</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 정자일로 121 지하 1층</t>
+          <t>경기도 성남시 분당구 내정로 58</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jamaica_bundang?igsh=MWY4cGIybjlodW11bw%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/ballydesign</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsknjve</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1841</v>
+        <v>237</v>
       </c>
       <c r="Q2" t="n">
-        <v>223</v>
+        <v>94</v>
       </c>
       <c r="R2" t="n">
-        <v>2064</v>
+        <v>331</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1710539074</t>
+          <t>158436174</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710539074</t>
+          <t>https://m.place.naver.com/place/158436174</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뉴핏휘트니스 정자점</t>
+          <t>비전휘트니스 분당점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>newfit_csj@naver.com</t>
+          <t>visionfitness555@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1347-6714</t>
+          <t>0507-1439-8755</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 정자로76번길 11 한라프라자</t>
+          <t>경기도 성남시 분당구 돌마로 46 광천프라자 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/newfit_csj</t>
+          <t>https://litt.ly/visionfitness05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,19 +695,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4k06n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1137</v>
+        <v>2471</v>
       </c>
       <c r="Q3" t="n">
-        <v>966</v>
+        <v>1919</v>
       </c>
       <c r="R3" t="n">
-        <v>2103</v>
+        <v>4390</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>36782451</t>
+          <t>1765794431</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36782451</t>
+          <t>https://m.place.naver.com/place/1765794431</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포짐 판교점</t>
+          <t>자마이카피트니스 분당정자점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spogym_2@naver.com</t>
+          <t>jamaica_jeongja@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1476-8384</t>
+          <t>0507-1383-8533</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+          <t>경기도 성남시 분당구 정자일로 121 지하 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_pg</t>
+          <t>https://www.instagram.com/jamaica_bundang?igsh=MWY4cGIybjlodW11bw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpasubw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>731</v>
+        <v>1841</v>
       </c>
       <c r="Q4" t="n">
-        <v>624</v>
+        <v>223</v>
       </c>
       <c r="R4" t="n">
-        <v>1355</v>
+        <v>2064</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20123697</t>
+          <t>1710539074</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20123697</t>
+          <t>https://m.place.naver.com/place/1710539074</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 야탑역점</t>
+          <t>그라운드피트니스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany90@naver.com</t>
+          <t>ground-fitness@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1337-9618</t>
+          <t>0507-1464-5758</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
+          <t>경기도 성남시 분당구 서현로 170 풍림아이원플러스 3층 301호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
+          <t>https://blog.naver.com/ground-fitness</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,19 +883,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5il7f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>706</v>
+        <v>374</v>
       </c>
       <c r="Q5" t="n">
-        <v>1494</v>
+        <v>1211</v>
       </c>
       <c r="R5" t="n">
-        <v>2200</v>
+        <v>1585</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1115298912</t>
+          <t>1472483345</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115298912</t>
+          <t>https://m.place.naver.com/place/1472483345</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,30 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>뭉트니스 야탑</t>
+          <t>익스홀릭 가넷 야탑점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mtns1@naver.com</t>
+          <t>exholic-yatop@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1486-1557</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 장미로 55 장미마을 지하1층</t>
+          <t>경기도 성남시 분당구 야탑로 95 세신옴니코아빌딩</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mtns_leader</t>
+          <t>http://익스홀릭가넷야탑점.shop/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1009,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>284</v>
+        <v>1960</v>
       </c>
       <c r="Q6" t="n">
-        <v>1036</v>
+        <v>1273</v>
       </c>
       <c r="R6" t="n">
-        <v>1320</v>
+        <v>3233</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1657314482</t>
+          <t>13581227</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657314482</t>
+          <t>https://m.place.naver.com/place/13581227</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1046,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
+          <t>업투 분당서현점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboy90_@naver.com</t>
+          <t>uptofitness5@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1419-2436</t>
+          <t>0507-1346-5229</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
+          <t>경기도 성남시 분당구 중앙공원로40번길 8 현대근린상가 지하1층 5호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy90_/223799590825</t>
+          <t>https://www.instagram.com/upto_seohyun/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,19 +1071,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wli4sqi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1107,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>457</v>
+        <v>1157</v>
       </c>
       <c r="Q7" t="n">
-        <v>751</v>
+        <v>723</v>
       </c>
       <c r="R7" t="n">
-        <v>1208</v>
+        <v>1880</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1989525945</t>
+          <t>1984136642</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989525945</t>
+          <t>https://m.place.naver.com/place/1984136642</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1139,34 +1123,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>크로스핏 테디짐 분당</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>cftdg@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1365-1447</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 정자일로198번길 15 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://www.instagram.com/teddygym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,22 +1165,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2540</v>
+        <v>395</v>
       </c>
       <c r="Q8" t="n">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="R8" t="n">
-        <v>2863</v>
+        <v>474</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>36406982</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/36406982</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>익스홀릭 가넷 미금점</t>
+          <t>밥스짐 분당점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dydwk147@naver.com</t>
+          <t>ish0674@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1429-2557</t>
+          <t>0507-1474-7017</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기도 성남시 분당구 성남대로 449 로얄팰리스 에이동 212, 213, 214호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dydwk147</t>
+          <t>https://www.instagram.com/bobsgymbob/profilecard/?igsh=MTFxcDRvanRsZ2ZyNA==</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,19 +1259,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4n5lk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>561</v>
+        <v>82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1074</v>
+        <v>185</v>
       </c>
       <c r="R9" t="n">
-        <v>1635</v>
+        <v>267</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>12763227</t>
+          <t>1581057750</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12763227</t>
+          <t>https://m.place.naver.com/place/1581057750</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,34 +1316,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>런던피트니스&amp;필라테스 분당이매점</t>
+          <t>투엑스휘트니스 분당점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
+          <t>2xfit@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1406-9679</t>
+          <t>031-782-5115</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+          <t>경기도 성남시 분당구 정자일로 177 분당인텔리지2 3F</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londoner83</t>
+          <t>http://www.2xfitness.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1382,14 +1358,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pnpp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1340</v>
+        <v>431</v>
       </c>
       <c r="Q10" t="n">
-        <v>473</v>
+        <v>28</v>
       </c>
       <c r="R10" t="n">
-        <v>1813</v>
+        <v>459</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>13530251</t>
+          <t>32278618</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13530251</t>
+          <t>https://m.place.naver.com/place/32278618</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1480,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wnvkt3b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1499,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>141</v>
+        <v>2540</v>
       </c>
       <c r="Q11" t="n">
-        <v>1437</v>
+        <v>323</v>
       </c>
       <c r="R11" t="n">
-        <v>1578</v>
+        <v>2863</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,15 +1482,767 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>엔엘휘트니스 분당이매점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>nlfitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1415-2075</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 440 지하1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nlfitness2_imae/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>642</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>241</v>
+      </c>
+      <c r="R12" t="n">
+        <v>883</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1194690742</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1194690742</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>헬스보이짐&amp;필라걸 수내점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>healthboy40@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1380-2239</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/healthboy40/223688037867</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>968</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>734</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1702</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1973151166</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1973151166</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>halogym02@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1315-8840</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/6/bizes/933331</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>663</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>929</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1592</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1806695299</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1806695299</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>피트니스비엠 분당 서현점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ksk2023@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1443-0942</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 482 주영빌딩 지하 1층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitnessbm._.hyoja</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>513</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>684</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1197</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>36333115</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36333115</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>베러댄 휘트니스 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>56zqrwcwsv@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1438-9698</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/56zqrwcwsv</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2085</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2467</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1013682807</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1013682807</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>쓰리핏PT 분당정자점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3fits@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1409-3559</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://3fitpt.com</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>800</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1157</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1845673431</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845673431</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>밀라노짐 수내점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>milanos_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1335-9682</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로166번길 5 원전빌딩 B1층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/milanogym_s</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1141</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>696</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1837</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1843911670</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1843911670</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>비율라이프 바디코치 여성전용 체형필라테스 PT 야탑점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>rockrock1256@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1445-2430</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로69번길 8 2층 바디코치 야탑점</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/official_bodycoach?igsh=MTF6cmlnd240MTdwMg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>786</v>
+      </c>
+      <c r="R19" t="n">
+        <v>989</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1723811790</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1723811790</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -1875,34 +1875,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>베러댄 휘트니스 분당야탑점</t>
+          <t>익스홀릭 가넷 수내점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>56zqrwcwsv@naver.com</t>
+          <t>garnetfit@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1438-9698</t>
+          <t>031-713-5355</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+          <t>경기도 성남시 분당구 내정로166번길 43 금산프라자 5층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/56zqrwcwsv</t>
+          <t>https://www.instagram.com/exholic_garnet</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>382</v>
+        <v>349</v>
       </c>
       <c r="Q16" t="n">
-        <v>2085</v>
+        <v>2022</v>
       </c>
       <c r="R16" t="n">
-        <v>2467</v>
+        <v>2371</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1013682807</t>
+          <t>11727876</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013682807</t>
+          <t>https://m.place.naver.com/place/11727876</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1969,39 +1969,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>쓰리핏PT 분당정자점</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3fits@naver.com</t>
+          <t>dydwk147@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1409-3559</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://3fitpt.com</t>
+          <t>https://blog.naver.com/dydwk147</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2022,7 +2022,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>357</v>
+        <v>561</v>
       </c>
       <c r="Q17" t="n">
-        <v>800</v>
+        <v>1074</v>
       </c>
       <c r="R17" t="n">
-        <v>1157</v>
+        <v>1635</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1845673431</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845673431</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2063,34 +2063,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>밀라노짐 수내점</t>
+          <t>스포애니 미금점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>milanos_1@naver.com</t>
+          <t>spoany_14s@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1335-9682</t>
+          <t>0507-1474-5855</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로166번길 5 원전빌딩 B1층</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 8층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/milanogym_s</t>
+          <t>https://www.instagram.com/spoany14/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1141</v>
+        <v>1083</v>
       </c>
       <c r="Q18" t="n">
-        <v>696</v>
+        <v>1817</v>
       </c>
       <c r="R18" t="n">
-        <v>1837</v>
+        <v>2900</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1843911670</t>
+          <t>20065928</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843911670</t>
+          <t>https://m.place.naver.com/place/20065928</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2157,34 +2157,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>비율라이프 바디코치 여성전용 체형필라테스 PT 야탑점</t>
+          <t>스포애니 야탑역점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rockrock1256@naver.com</t>
+          <t>spoany90@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1445-2430</t>
+          <t>0507-1337-9618</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 8 2층 바디코치 야탑점</t>
+          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/official_bodycoach?igsh=MTF6cmlnd240MTdwMg%3D%3D&amp;utm_source=qr</t>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2219,30 +2219,5376 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>707</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1494</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2201</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1115298912</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1115298912</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>F45 정자</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로198번길 24 2층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/f45_jeongja</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>42</v>
+      </c>
+      <c r="R20" t="n">
+        <v>159</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1893893702</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1893893702</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>londoner83@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1406-9679</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/londoner83</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1340</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>473</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1813</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>13530251</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13530251</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 오리역점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1364-3711</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 구미로 5 1~4층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=76</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>824</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>51</v>
+      </c>
+      <c r="R22" t="n">
+        <v>875</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2087270892</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2087270892</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>트랜스핏짐 서현역점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>transfit_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1387-9682</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당로53번길 15 지하1층 트랜스핏짐 서현역점</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/transfit_gym</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>2191</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2246</v>
+      </c>
+      <c r="R23" t="n">
+        <v>4437</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1487183442</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1487183442</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>제이치피트니스 헬스&amp;PT 미금점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>redgym_migeum@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1332-4462</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 165 지하1층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jhfitness_migeum?igsh</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1284</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>274</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1558</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1109176574</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1109176574</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>뉴핏휘트니스 정자점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>newfit_csj@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1347-6714</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자로76번길 11 한라프라자</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/newfit_csj</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1137</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>966</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2103</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>36782451</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36782451</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>미켈란 스포츠 센터</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>michelansports@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>michelansports@gmail.com</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1383-1163</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 100 미켈란쉐르빌 3층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>http://www.michelansports.com</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>475</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>852</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1327</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1239062727</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1239062727</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>스포애니 서현역점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>spoany22@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>031-706-8522</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany22</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>950</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2036</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2986</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>13025013</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13025013</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>쓰리핏 헬스&amp;PT 서현점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3fits@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1388-2211</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 불정로 379 서현프라자 지하1층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://3fitpt.com</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1029</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>929</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1958</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1181952796</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1181952796</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>kindgym28@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1361-3615</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로81번길 10 아미고타워 B1층 카인드짐 휘트니스 헬스&amp;PT 야탑역점</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kindgym28</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>2034</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1577</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3611</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>36230651</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36230651</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>스포짐 판교역점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>showmethecash@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1436-1236</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spogym_p.g/</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>1252</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>641</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1893</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1088507385</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088507385</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>피트니스웰시 헬스&amp;PT 분당정자점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>health-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1489-7037</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로343번길 12-8 1동 4층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/health-pt</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>531</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>469</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1623406875</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1623406875</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>짐라이언피트니스 수내역1호점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>liongym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1319-1102</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 수내로46번길 11 지하1층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gymlion_sunae</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>1701</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>343</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2044</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1628575924</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628575924</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>클럽 브릭스 판교</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>club_breex@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>031-625-5566</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당내곡로 131 판교테크원타워 B1 클럽브릭스</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/club_breex</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>94</v>
+      </c>
+      <c r="R33" t="n">
+        <v>425</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1141858723</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1141858723</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>뭉트니스 야탑</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>mtns1@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mtns_leader</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1036</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1320</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1657314482</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1657314482</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>밀라노짐 야탑점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3989753@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 471 4층 밀라노짐 야탑점</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/3989753</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>335</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>600</v>
+      </c>
+      <c r="R35" t="n">
+        <v>935</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>21638305</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21638305</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>빌리프짐 헬스&amp;PT 분당</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>beliefgym007@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 미금로 45 진도훼미리프라자 5층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/beliefgym007</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1360</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>650</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2010</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1800773799</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1800773799</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>헬스플러스 판교5호점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>healthplus_pangyo5@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1313-1507</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 2 지하1층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/healthplus_pangyo5/</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>674</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1070</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1744</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1086359388</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1086359388</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>하이클래스짐 서현점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>highclassgym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 불정로 382 3층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/highclassgym2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>1336</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1814</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3150</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1974917013</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1974917013</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>피트니스비엠 분당 장안타운점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>fitnessbm77@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1397-6556</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당로263번길 35 서현굿모닝프라자</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessbm77</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>786</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1065</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>20099119</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20099119</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>고릴라멀티짐 분당서현점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>gorillagym6@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1373-0880</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로 192 야베스벨리 5층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gorillamultigym_bundangseohyun?igsh=cWMyMDFqYjZsdjg5&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>652</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>949</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1601</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>31457116</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31457116</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>바이칼휘트니스 서현지점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>kes90427@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1309-7941</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 중앙공원로40번길 4 현대카스올림픽골프파크 b1층 바이칼휘트니스</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/baikal_seohyun?igsh=bW9hMnRieGVnZmM5</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>472</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2972</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>65708757</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/65708757</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>렛츠핏 야탑점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>sm8893@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1305-0298</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 벌말로 37 4층 1, 2호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://bmarket.broj.co.kr/groups/413620357</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>916</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1289</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2205</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1320604673</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1320604673</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>healthboy90_@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1419-2436</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/healthboy90_/223799590825</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>457</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>751</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1208</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1989525945</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1989525945</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>버핏그라운드 판교</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1329-4325</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://pt.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>1765</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>250</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2015</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1136752576</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1136752576</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>크로스핏 라운지</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>crossfit_lounge@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1321-6851</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로319번길 8-4 지하1층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/crossfit_lounge</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>271</v>
+      </c>
+      <c r="R45" t="n">
+        <v>314</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2067270233</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2067270233</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>F45 서현</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>yerim1118@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>031-702-4520</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로342번길 21 대정빌딩 지하 1층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/f45_seohyeon/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>468</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>96</v>
+      </c>
+      <c r="R46" t="n">
+        <v>564</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1316630678</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1316630678</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>일론짐 X 메루치양식장 야탑점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>elon_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1333-9116</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로69번길 8 한주코아 제상가동 제지하층 제비01호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/elon.gym/</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>546</v>
+      </c>
+      <c r="R47" t="n">
+        <v>684</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1213835536</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213835536</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>원팀짐</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>oneteamgym-@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>031-702-2070</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oneteamgym1</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>492</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>289</v>
+      </c>
+      <c r="R48" t="n">
+        <v>781</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1973455447</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1973455447</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>파크뷰휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>parkviewf1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>parkview.f.1004@gmail.com</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>031-783-3000</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 248 파크뷰상가 3층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.parkviewfc.co.kr</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>127</v>
+      </c>
+      <c r="R49" t="n">
+        <v>175</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>11847077</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11847077</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>와이피트니스 헬스&amp;PT 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>yfitness02@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1430-1729</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 벌말로40번길 5-1 지하1층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yfitness02?igsh=MTR6dDl6cW5sNWNxMg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>55</v>
+      </c>
+      <c r="R50" t="n">
+        <v>160</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2013735870</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2013735870</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>밀라노짐 정자점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>milanogymj@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1327-2562</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 162 젤존타워2 502호 밀라노짐</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/milanogym_j</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>757</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1489</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2246</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1641679909</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1641679909</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>스포애니 수내점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>spoany012@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>031-712-3362</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 364 현대제일상가 B1층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://m.spoany.co.kr/branch/branch_detail.html?base_seq=MjE=</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1548</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1844</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>31849989</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31849989</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>빌드업피트니스 PT 야탑점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>buildupfitness02@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1329-7003</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 장미로 198 B1 빌드업피트니스PT 야탑점</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.buildupfitness.co.kr</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>2434</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1016</v>
+      </c>
+      <c r="R53" t="n">
+        <v>3450</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1233503897</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1233503897</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>스포짐 판교점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>spogym_2@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1476-8384</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spogym_pg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>731</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>623</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1354</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>20123697</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20123697</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>업투휘트니스 분당삼평점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>upto_sampyeong@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1466-1103</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 375 4층 401-2,402~405호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/upto_sampyeong</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>562</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>555</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1117</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1878300058</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1878300058</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>팀버핏 판교</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하3층 B3008</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/butfitground</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>95</v>
+      </c>
+      <c r="R56" t="n">
+        <v>331</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1004612269</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1004612269</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>스타디온 판교 크로스핏</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>sbkim10@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>031-603-1109</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로177번길 25 지하B103호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stadion_pangyo_crossfit?igsh=MXg2azI4ZjFsemtkMw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>326</v>
+      </c>
+      <c r="R57" t="n">
+        <v>440</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1332230479</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332230479</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>베러댄 휘트니스 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>56zqrwcwsv@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1438-9698</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/56zqrwcwsv</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2085</v>
+      </c>
+      <c r="R58" t="n">
+        <v>2467</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1013682807</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1013682807</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>쓰리핏PT 분당정자점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3fits@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1409-3559</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로113번길 4 2층 202호, 203-1호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://3fitpt.com</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>800</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1157</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1845673431</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845673431</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>밀라노짐 수내점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>milanos_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1335-9682</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로166번길 5 원전빌딩 B1층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/milanogym_s</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1141</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>696</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1837</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1843911670</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1843911670</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>비율라이프 바디코치 여성전용 체형필라테스 PT 야탑점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>rockrock1256@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1445-2430</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로69번길 8 2층 바디코치 야탑점</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/official_bodycoach?igsh=MTF6cmlnd240MTdwMg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
         <v>203</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q61" t="n">
         <v>786</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R61" t="n">
         <v>989</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
         <is>
           <t>1723811790</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1723811790</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>피티세븐 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>body2balance@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1400-9428</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>http://www.pts7.com</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>291</v>
+      </c>
+      <c r="R62" t="n">
+        <v>593</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>13093618</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13093618</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>험블 휘트니스 PT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>humblefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>031-697-8768</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/humblefitness</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1437</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1578</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1134171602</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1134171602</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>업투 휘트니스 분당판교점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>uptofitness-@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1343-8274</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/uptofitness-</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>618</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>291</v>
+      </c>
+      <c r="R64" t="n">
+        <v>909</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1928497638</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928497638</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>쓰리핏 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3fits@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1302-3558</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 돌마로 47 6층 607호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://3fitpt.com</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>427</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>954</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1381</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1135214262</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1135214262</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>와이짐 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ygym3018@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1325-3018</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 165 2층 223호, 224호 와이짐 PT 분당미금점</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ygym3018</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>1077</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>445</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1522</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1598086500</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1598086500</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>브레이브 휘트니스 분당정자점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>bravefitness_jeongja@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1484-0779</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로17번길 2 지하1층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bravefitness_jeongja</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1418</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1221</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2639</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1043618213</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1043618213</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>와이투짐 야탑역점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>y2gym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1352-8844</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 912 B1층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/y2gym2</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>380</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1572</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1952</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1930702763</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1930702763</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>크레이지핏 PT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>krazyfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1488-5883</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>535</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1437</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1972</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1628554288</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628554288</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>데스런 판교점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>deslun@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1412-6347</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>http://www.deslun.co.kr</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>395</v>
+      </c>
+      <c r="R70" t="n">
+        <v>417</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>31469573</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31469573</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>올뉴바디 운동맛집PT 야탑점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>allnewbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1329-3987</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 벌말로 44 401호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/allnewbody</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>618</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1218</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1203378061</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1203378061</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>제로업PT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>axus2000@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>031-623-2775</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 16 7층</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/zero____up/</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>767</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>709</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1476</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1975822360</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1975822360</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>리조트휘트니스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>resort_5@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1438-0677</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>714</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1127</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>35524502</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35524502</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>팀제이맥스 피티 서현점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>teamjmax_sh@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>031-702-8296</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teamjmax_sh</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>911</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>549</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1460</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1639683746</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639683746</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>솔리드짐 PT 수내점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ppapers@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1420-7858</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/solid_gym1</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>652</v>
+      </c>
+      <c r="R75" t="n">
+        <v>797</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1205679892</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1205679892</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>리파인짐 PT 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ksw8591@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1380-1864</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로926번길 6 302호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ksw8591</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>310</v>
+      </c>
+      <c r="R76" t="n">
+        <v>452</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1297851351</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1297851351</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jamaica_bundang?igsh=MWY4cGIybjlodW11bw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsknjve</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -650,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뉴핏휘트니스 정자점</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>newfit_csj@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1347-6714</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자로76번길 11 한라프라자</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4k06n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1137</v>
+        <v>2540</v>
       </c>
       <c r="Q3" t="n">
-        <v>966</v>
+        <v>323</v>
       </c>
       <c r="R3" t="n">
-        <v>2103</v>
+        <v>2863</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>36782451</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36782451</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포짐 판교점</t>
+          <t>뉴핏휘트니스 정자점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spogym7@naver.com</t>
+          <t>newfit_csj@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1476-8384</t>
+          <t>0507-1347-6714</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+          <t>경기도 성남시 분당구 정자로76번길 11 한라프라자</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/newfit_csj</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,24 +784,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpasubw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>731</v>
+        <v>1137</v>
       </c>
       <c r="Q4" t="n">
-        <v>623</v>
+        <v>966</v>
       </c>
       <c r="R4" t="n">
-        <v>1354</v>
+        <v>2103</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20123697</t>
+          <t>36782451</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20123697</t>
+          <t>https://m.place.naver.com/place/36782451</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 야탑역점</t>
+          <t>스포짐 판교점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany90@naver.com</t>
+          <t>spogym_2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1337-9618</t>
+          <t>0507-1476-8384</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
+          <t>https://www.instagram.com/spogym_pg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5il7f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="Q5" t="n">
-        <v>1499</v>
+        <v>623</v>
       </c>
       <c r="R5" t="n">
-        <v>2206</v>
+        <v>1354</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1115298912</t>
+          <t>20123697</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115298912</t>
+          <t>https://m.place.naver.com/place/20123697</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>스포애니 야탑역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>spoany90@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1337-9618</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2540</v>
+        <v>707</v>
       </c>
       <c r="Q6" t="n">
-        <v>323</v>
+        <v>1499</v>
       </c>
       <c r="R6" t="n">
-        <v>2863</v>
+        <v>2206</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1115298912</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1115298912</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1052,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mtns_leader</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1062,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1110,10 +1090,10 @@
         <v>284</v>
       </c>
       <c r="Q7" t="n">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="R7" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1132,7 +1112,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1190,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42raj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1234,7 +1210,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>런던피트니스&amp;필라테스 분당이매점</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
+          <t>dydwk147@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1406-9679</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dydwk147</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,24 +1254,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pnpp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1340</v>
+        <v>561</v>
       </c>
       <c r="Q9" t="n">
-        <v>473</v>
+        <v>1075</v>
       </c>
       <c r="R9" t="n">
-        <v>1813</v>
+        <v>1636</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13530251</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13530251</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>londoner83@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1406-9679</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/londoner83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,24 +1348,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wnvkt3b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>141</v>
+        <v>1340</v>
       </c>
       <c r="Q10" t="n">
-        <v>1437</v>
+        <v>473</v>
       </c>
       <c r="R10" t="n">
-        <v>1578</v>
+        <v>1813</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>13530251</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/13530251</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>원팀짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
+          <t>oneteamgym-@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1402-7136</t>
+          <t>031-702-2070</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/oneteamgym1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,7 +1442,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1484,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc9u20</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1499,17 +1463,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>54</v>
+        <v>493</v>
       </c>
       <c r="Q11" t="n">
-        <v>107</v>
+        <v>289</v>
       </c>
       <c r="R11" t="n">
-        <v>161</v>
+        <v>782</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1482,205 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>36428321</t>
+          <t>1973455447</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428321</t>
+          <t>https://m.place.naver.com/place/1973455447</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>투엑스휘트니스 분당점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2xfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>031-782-5115</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 177 분당인텔리지2 3F</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>http://www.2xfitness.co.kr/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>431</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>28</v>
+      </c>
+      <c r="R12" t="n">
+        <v>459</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>32278618</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32278618</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>채움필라테스</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>chaeum_pilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1318-4137</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기 성남시 분당구 돌마로486번길 6 상록프라자 4층 채움필라테스</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>48</v>
+      </c>
+      <c r="R13" t="n">
+        <v>101</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1101909057</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1101909057</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>메이크어바디 헬스 PT 미금점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>makeabody1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1407-3242</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 돌마로 67 5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://www.instagram.com/make_a__body</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2540</v>
+        <v>474</v>
       </c>
       <c r="Q3" t="n">
-        <v>323</v>
+        <v>782</v>
       </c>
       <c r="R3" t="n">
-        <v>2863</v>
+        <v>1256</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1315101138</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1315101138</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +747,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>뉴핏휘트니스 정자점</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>newfit_csj@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1347-6714</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자로76번길 11 한라프라자</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/newfit_csj</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1137</v>
+        <v>2540</v>
       </c>
       <c r="Q4" t="n">
-        <v>966</v>
+        <v>323</v>
       </c>
       <c r="R4" t="n">
-        <v>2103</v>
+        <v>2863</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36782451</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36782451</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -906,10 +906,10 @@
         <v>731</v>
       </c>
       <c r="Q5" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="R5" t="n">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>707</v>
       </c>
       <c r="Q6" t="n">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="R6" t="n">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1222,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>익스홀릭 가넷 미금점</t>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dydwk147@naver.com</t>
+          <t>londoner83@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1429-2557</t>
+          <t>0507-1406-9679</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dydwk147</t>
+          <t>https://blog.naver.com/londoner83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>561</v>
+        <v>1340</v>
       </c>
       <c r="Q9" t="n">
-        <v>1075</v>
+        <v>473</v>
       </c>
       <c r="R9" t="n">
-        <v>1636</v>
+        <v>1813</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>12763227</t>
+          <t>13530251</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12763227</t>
+          <t>https://m.place.naver.com/place/13530251</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,39 +1311,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>런던피트니스&amp;필라테스 분당이매점</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1406-9679</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londoner83</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1364,7 +1368,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1340</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1813</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>13530251</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13530251</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1409,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>원팀짐</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>oneteamgym-@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-702-2070</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneteamgym1</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>493</v>
+        <v>141</v>
       </c>
       <c r="Q11" t="n">
-        <v>289</v>
+        <v>1437</v>
       </c>
       <c r="R11" t="n">
-        <v>782</v>
+        <v>1578</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,203 +1486,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1973455447</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973455447</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>투엑스휘트니스 분당점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2xfit@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>031-782-5115</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 정자일로 177 분당인텔리지2 3F</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>http://www.2xfitness.co.kr/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>431</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>28</v>
-      </c>
-      <c r="R12" t="n">
-        <v>459</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>32278618</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/32278618</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>채움필라테스</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>chaeum_pilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1318-4137</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기 성남시 분당구 돌마로486번길 6 상록프라자 4층 채움필라테스</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>48</v>
-      </c>
-      <c r="R13" t="n">
-        <v>101</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1101909057</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1101909057</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jamaica_bundang?igsh=MWY4cGIybjlodW11bw%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsknjve</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="Q2" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="R2" t="n">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -680,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/make_a__body</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4s9yg</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Q3" t="n">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="R3" t="n">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -747,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>스포짐 판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>spogym7@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1476-8384</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +792,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpasubw</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2540</v>
+        <v>731</v>
       </c>
       <c r="Q4" t="n">
-        <v>323</v>
+        <v>624</v>
       </c>
       <c r="R4" t="n">
-        <v>2863</v>
+        <v>1355</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>20123697</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/20123697</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포짐 판교점</t>
+          <t>스포애니 야탑역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spogym_2@naver.com</t>
+          <t>spoany90@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1476-8384</t>
+          <t>0507-1337-9618</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_pg</t>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5il7f</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="Q5" t="n">
-        <v>624</v>
+        <v>1499</v>
       </c>
       <c r="R5" t="n">
-        <v>1355</v>
+        <v>2206</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20123697</t>
+          <t>1115298912</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20123697</t>
+          <t>https://m.place.naver.com/place/1115298912</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,34 +951,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 야탑역점</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany90@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1337-9618</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +988,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>707</v>
+        <v>2541</v>
       </c>
       <c r="Q6" t="n">
-        <v>1500</v>
+        <v>323</v>
       </c>
       <c r="R6" t="n">
-        <v>2207</v>
+        <v>2864</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1115298912</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115298912</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1052,7 +1072,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mtns_leader</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1062,7 +1082,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1090,10 +1110,10 @@
         <v>284</v>
       </c>
       <c r="Q7" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="R7" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1170,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42raj</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1244,7 +1268,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londoner83</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,20 +1278,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pnpp</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,64 +1339,64 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>피트니스 리본</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>fitnessreborn@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1417-1133</t>
+          <t>0507-1376-1546</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기도 성남시 분당구 매화로 53 5층 피트니스리본</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wumh0ut</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1377,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>1155595700</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/1155595700</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>짐휴 PT 분당미금점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>gym_hue@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1369-1180</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 5층 509호, 510호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1446,20 +1474,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w486ct</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1471,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>141</v>
+        <v>186</v>
       </c>
       <c r="Q11" t="n">
-        <v>1437</v>
+        <v>247</v>
       </c>
       <c r="R11" t="n">
-        <v>1578</v>
+        <v>433</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,15 +1518,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1527774793</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1527774793</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>베스트바디발란스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>wjdwktnso@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1402-7136</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc9u20</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>107</v>
+      </c>
+      <c r="R12" t="n">
+        <v>161</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>36428321</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36428321</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="Q2" t="n">
         <v>224</v>
       </c>
       <c r="R2" t="n">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/make_a__body</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4s9yg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -748,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -760,24 +756,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포짐 판교점</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spogym7@naver.com</t>
+          <t>dydwk147@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1476-8384</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wpasubw</t>
+          <t>https://talk.naver.com/ct/w4n5lk</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>731</v>
+        <v>562</v>
       </c>
       <c r="Q4" t="n">
-        <v>624</v>
+        <v>1075</v>
       </c>
       <c r="R4" t="n">
-        <v>1355</v>
+        <v>1637</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20123697</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20123697</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -858,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 야탑역점</t>
+          <t>스포짐 판교점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany90@naver.com</t>
+          <t>spogym7@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1337-9618</t>
+          <t>0507-1476-8384</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -905,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5il7f</t>
+          <t>https://talk.naver.com/ct/wpasubw</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="Q5" t="n">
-        <v>1499</v>
+        <v>624</v>
       </c>
       <c r="R5" t="n">
-        <v>2206</v>
+        <v>1355</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,51 +930,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1115298912</t>
+          <t>20123697</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115298912</t>
+          <t>https://m.place.naver.com/place/20123697</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>스포애니 야탑역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>spoany90@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1337-9618</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 성남대로 926 메트로빌딩 8층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
+          <t>https://talk.naver.com/ct/w5il7f</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2541</v>
+        <v>708</v>
       </c>
       <c r="Q6" t="n">
-        <v>323</v>
+        <v>1503</v>
       </c>
       <c r="R6" t="n">
-        <v>2864</v>
+        <v>2211</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,42 +1028,46 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1115298912</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1115298912</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>뭉트니스 야탑</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mtns1@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1402-1275</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1092,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1107,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>284</v>
+        <v>2543</v>
       </c>
       <c r="Q7" t="n">
-        <v>1036</v>
+        <v>323</v>
       </c>
       <c r="R7" t="n">
-        <v>1320</v>
+        <v>2866</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1657314482</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657314482</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1144,33 +1148,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>뭉트니스 야탑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1329-4325</t>
-        </is>
-      </c>
+          <t>mtns1@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,27 +1176,23 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42raj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1765</v>
+        <v>284</v>
       </c>
       <c r="Q8" t="n">
-        <v>250</v>
+        <v>1036</v>
       </c>
       <c r="R8" t="n">
-        <v>2015</v>
+        <v>1320</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1657314482</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1657314482</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1238,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>런던피트니스&amp;필라테스 분당이매점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1406-9679</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,12 +1274,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,12 +1289,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pnpp</t>
+          <t>https://talk.naver.com/ct/w42raj</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1340</v>
+        <v>1765</v>
       </c>
       <c r="Q9" t="n">
-        <v>473</v>
+        <v>250</v>
       </c>
       <c r="R9" t="n">
-        <v>1813</v>
+        <v>2015</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13530251</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13530251</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1362,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitnessreborn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,24 +1372,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wumh0ut</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1430,7 +1422,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1442,24 +1434,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐휴 PT 분당미금점</t>
+          <t>쿼드짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gym_hue@naver.com</t>
+          <t>quadgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1369-1180</t>
+          <t>0507-1303-9415</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 5층 509호, 510호</t>
+          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1489,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w486ct</t>
+          <t>https://talk.naver.com/ct/wc5w2o</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Q11" t="n">
-        <v>247</v>
+        <v>102</v>
       </c>
       <c r="R11" t="n">
-        <v>433</v>
+        <v>184</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1510,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1527774793</t>
+          <t>1759307500</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527774793</t>
+          <t>https://m.place.naver.com/place/1759307500</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1540,24 +1532,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>석세스짐&amp;PT 분당무지개마을점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
+          <t>successgym-b3@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1402-7136</t>
+          <t>0507-1331-7127</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 미금로 36 브리엘프라자 4층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1587,7 +1579,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc9u20</t>
+          <t>https://talk.naver.com/ct/w45gyo</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1597,17 +1589,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="Q12" t="n">
-        <v>107</v>
+        <v>336</v>
       </c>
       <c r="R12" t="n">
-        <v>161</v>
+        <v>439</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,17 +1608,115 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>36428321</t>
+          <t>1860293712</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428321</t>
+          <t>https://m.place.naver.com/place/1860293712</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H GYM PT GT 판교2호점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1353-9408</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://hgym.imweb.me</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47alh</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>421</v>
+      </c>
+      <c r="R13" t="n">
+        <v>700</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1850894755</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850894755</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jamaica_bundang?igsh=MWY4cGIybjlodW11bw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsknjve</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1845</v>
+        <v>1848</v>
       </c>
       <c r="Q2" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="R2" t="n">
-        <v>2069</v>
+        <v>2073</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>익스홀릭 가넷 미금점</t>
+          <t>스포짐 판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dydwk147@naver.com</t>
+          <t>spogym_2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1429-2557</t>
+          <t>0507-1476-8384</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/spogym_pg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -798,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4n5lk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>562</v>
+        <v>731</v>
       </c>
       <c r="Q4" t="n">
-        <v>1075</v>
+        <v>624</v>
       </c>
       <c r="R4" t="n">
-        <v>1637</v>
+        <v>1355</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>12763227</t>
+          <t>20123697</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12763227</t>
+          <t>https://m.place.naver.com/place/20123697</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -849,34 +841,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포짐 판교점</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spogym7@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1476-8384</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,24 +878,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpasubw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>731</v>
+        <v>2543</v>
       </c>
       <c r="Q5" t="n">
-        <v>624</v>
+        <v>323</v>
       </c>
       <c r="R5" t="n">
-        <v>1355</v>
+        <v>2866</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20123697</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20123697</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -994,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5il7f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="Q6" t="n">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="R6" t="n">
-        <v>2211</v>
+        <v>2217</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1045,34 +1029,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,27 +1070,23 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2543</v>
+        <v>1766</v>
       </c>
       <c r="Q7" t="n">
-        <v>323</v>
+        <v>250</v>
       </c>
       <c r="R7" t="n">
-        <v>2866</v>
+        <v>2016</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,25 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>뭉트니스 야탑</t>
+          <t>헬스보이짐&amp;필라걸&amp;골프인 분당정자점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mtns1@naver.com</t>
+          <t>healthboy90_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1419-2436</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 55 장미마을 지하1층</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 7층 701-706호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthboy90_/223799590825</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,12 +1164,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1201,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>284</v>
+        <v>457</v>
       </c>
       <c r="Q8" t="n">
-        <v>1036</v>
+        <v>756</v>
       </c>
       <c r="R8" t="n">
-        <v>1320</v>
+        <v>1213</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1657314482</t>
+          <t>1989525945</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657314482</t>
+          <t>https://m.place.naver.com/place/1989525945</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,33 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>londoner83@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1406-9679</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/londoner83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1284,17 +1268,13 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42raj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1765</v>
+        <v>1341</v>
       </c>
       <c r="Q9" t="n">
-        <v>250</v>
+        <v>473</v>
       </c>
       <c r="R9" t="n">
-        <v>2015</v>
+        <v>1814</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>13530251</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/13530251</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1335,34 +1315,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>피트니스 리본</t>
+          <t>짐휴 PT 분당미금점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitnessreborn@naver.com</t>
+          <t>gym_hue@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1376-1546</t>
+          <t>0507-1369-1180</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 매화로 53 5층 피트니스리본</t>
+          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 5층 509호, 510호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessreborn</t>
+          <t>https://www.instagram.com/gym_hue</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1397,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>505</v>
+        <v>187</v>
       </c>
       <c r="Q10" t="n">
-        <v>89</v>
+        <v>247</v>
       </c>
       <c r="R10" t="n">
-        <v>594</v>
+        <v>434</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1155595700</t>
+          <t>1527774793</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155595700</t>
+          <t>https://m.place.naver.com/place/1527774793</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1456,7 +1436,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/quadgym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1466,24 +1446,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc5w2o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1519,202 +1495,6 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>석세스짐&amp;PT 분당무지개마을점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>successgym-b3@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1331-7127</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 미금로 36 브리엘프라자 4층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45gyo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>103</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>336</v>
-      </c>
-      <c r="R12" t="n">
-        <v>439</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1860293712</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1860293712</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>H GYM PT GT 판교2호점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>hgym9408@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1353-9408</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://hgym.imweb.me</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47alh</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>279</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>421</v>
-      </c>
-      <c r="R13" t="n">
-        <v>700</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1850894755</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -423,10 +423,10 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1848</v>
+        <v>1853</v>
       </c>
       <c r="Q2" t="n">
         <v>225</v>
       </c>
       <c r="R2" t="n">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="Q5" t="n">
         <v>323</v>
       </c>
       <c r="R5" t="n">
-        <v>2866</v>
+        <v>2868</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1000,10 +1000,10 @@
         <v>710</v>
       </c>
       <c r="Q6" t="n">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="R6" t="n">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>partner@butfitseoul.com</t>
+          <t>butfitseoul@butfitseoul.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1226,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>런던피트니스&amp;필라테스 분당이매점</t>
+          <t>그라운드피트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
+          <t>ground-fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1406-9679</t>
+          <t>0507-1464-5758</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+          <t>경기도 성남시 분당구 서현로 170 풍림아이원플러스 3층 301호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londoner83</t>
+          <t>https://blog.naver.com/ground-fitness</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1341</v>
+        <v>374</v>
       </c>
       <c r="Q9" t="n">
-        <v>473</v>
+        <v>1219</v>
       </c>
       <c r="R9" t="n">
-        <v>1814</v>
+        <v>1593</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1298,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13530251</t>
+          <t>1472483345</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13530251</t>
+          <t>https://m.place.naver.com/place/1472483345</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐휴 PT 분당미금점</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gym_hue@naver.com</t>
+          <t>dydwk147@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1369-1180</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 5층 509호, 510호</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_hue</t>
+          <t>https://blog.naver.com/dydwk147</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>187</v>
+        <v>562</v>
       </c>
       <c r="Q10" t="n">
-        <v>247</v>
+        <v>1078</v>
       </c>
       <c r="R10" t="n">
-        <v>434</v>
+        <v>1640</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1527774793</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527774793</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1414,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>쿼드짐</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>quadgym@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1303-9415</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/quadgym</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="Q11" t="n">
-        <v>102</v>
+        <v>1437</v>
       </c>
       <c r="R11" t="n">
-        <v>184</v>
+        <v>1578</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/분당_헬스장.xlsx
+++ b/naver-place-crawler/results_health/분당_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -812,10 +812,10 @@
         <v>731</v>
       </c>
       <c r="Q4" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="R4" t="n">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>710</v>
       </c>
       <c r="Q6" t="n">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="R6" t="n">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>butfitseoul@butfitseoul.com</t>
+          <t>partner@butfitseoul.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1226,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>그라운드피트니스</t>
+          <t>익스홀릭 가넷 미금점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ground-fitness@naver.com</t>
+          <t>dydwk147@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1464-5758</t>
+          <t>0507-1429-2557</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 풍림아이원플러스 3층 301호</t>
+          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ground-fitness</t>
+          <t>https://blog.naver.com/dydwk147</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>374</v>
+        <v>562</v>
       </c>
       <c r="Q9" t="n">
-        <v>1219</v>
+        <v>1079</v>
       </c>
       <c r="R9" t="n">
-        <v>1593</v>
+        <v>1641</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1472483345</t>
+          <t>12763227</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472483345</t>
+          <t>https://m.place.naver.com/place/12763227</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>익스홀릭 가넷 미금점</t>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dydwk147@naver.com</t>
+          <t>londoner83@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1429-2557</t>
+          <t>0507-1406-9679</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 87 골드프라자 6층 가넷휘트니스</t>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dydwk147</t>
+          <t>https://blog.naver.com/londoner83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>562</v>
+        <v>1342</v>
       </c>
       <c r="Q10" t="n">
-        <v>1078</v>
+        <v>473</v>
       </c>
       <c r="R10" t="n">
-        <v>1640</v>
+        <v>1815</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>12763227</t>
+          <t>13530251</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12763227</t>
+          <t>https://m.place.naver.com/place/13530251</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>짐휴 PT 분당미금점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>gym_hue@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1369-1180</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 5층 509호, 510호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://www.instagram.com/gym_hue</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="Q11" t="n">
-        <v>1437</v>
+        <v>247</v>
       </c>
       <c r="R11" t="n">
-        <v>1578</v>
+        <v>434</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,15 +1486,109 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1527774793</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1527774793</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>더바디짐 PT 분당수내점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>thebodyptgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1387-7676</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 수내로46번길 11 대덕글로리빌딩 5층 더바디짐</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thebodyptgym</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1712</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1865</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>36666737</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36666737</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
